--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D9317C-52B6-4D2D-B2AD-6BE25176A17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9C3B72-04BD-4ED3-80F6-019DED446BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5820" yWindow="8260" windowWidth="30590" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,17 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PopularityData</t>
-  </si>
-  <si>
-    <t>(list#sep=/),TbPopularityData#sep=+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人气选手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>datetime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,6 +92,37 @@
   </si>
   <si>
     <t>Exhibition+ExhibitionOneDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CG_05.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CG_06.png</t>
+  </si>
+  <si>
+    <t>ExposureDeftual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础曝光值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -152,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -160,10 +180,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -444,115 +460,139 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="20.08203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="39.4140625" customWidth="1"/>
-    <col min="6" max="7" width="77.1640625" customWidth="1"/>
+    <col min="3" max="4" width="20.08203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="39.4140625" customWidth="1"/>
+    <col min="7" max="7" width="77.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="2">
         <v>46023</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>17</v>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1">
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="2">
         <v>46024</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="13.5" customHeight="1">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="13.5" customHeight="1">
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9C3B72-04BD-4ED3-80F6-019DED446BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC049F5-C2F4-4F6C-B393-910D824DD73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5020" yWindow="1450" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -109,9 +109,6 @@
   <si>
     <t>CG_05.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CG_06.png</t>
   </si>
   <si>
     <t>ExposureDeftual</t>
@@ -490,7 +487,7 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -513,7 +510,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -536,7 +533,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -567,7 +564,7 @@
         <v>46024</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC049F5-C2F4-4F6C-B393-910D824DD73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0742EA-7C07-4764-AFC4-A910626F2D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5020" yWindow="1450" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,7 +541,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>20</v>
@@ -561,7 +561,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0742EA-7C07-4764-AFC4-A910626F2D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501A17E6-D99C-41F3-8E6D-20B83D28FE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5020" yWindow="1450" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3250" yWindow="2500" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,15 +111,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ExposureDeftual</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础曝光值</t>
+    <t>TargetClothingID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标服装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AdditionValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加成值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -457,17 +465,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="4" width="20.08203125" customWidth="1"/>
     <col min="5" max="5" width="30.83203125" customWidth="1"/>
     <col min="6" max="6" width="39.4140625" customWidth="1"/>
-    <col min="7" max="7" width="77.1640625" customWidth="1"/>
+    <col min="7" max="7" width="23.9140625" customWidth="1"/>
+    <col min="8" max="8" width="17.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,8 +498,11 @@
       <c r="G1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -510,10 +522,13 @@
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -533,10 +548,13 @@
         <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -553,10 +571,13 @@
         <v>16</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1">
+        <v>10001</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -573,20 +594,23 @@
         <v>16</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13.5" customHeight="1">
+        <v>10001</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="13.5" customHeight="1">
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -1,152 +1,178 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501A17E6-D99C-41F3-8E6D-20B83D28FE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3250" yWindow="2500" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>##var</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>StartDateTime</t>
+  </si>
+  <si>
+    <t>IconName</t>
+  </si>
+  <si>
+    <t>ExhibitionInfoName</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>TargetClothingID</t>
+  </si>
+  <si>
+    <t>AdditionValue</t>
+  </si>
+  <si>
+    <t>ExhibitionTargetFans</t>
   </si>
   <si>
     <t>##type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>TbLocalzationKeyData#sep=+</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>唯一标识符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartDateTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>开启时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbLocalzationKeyData#sep=+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片名字</t>
+  </si>
+  <si>
+    <t>展会名称</t>
   </si>
   <si>
     <t>展会描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExhibitionInfoName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>展会名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>datetime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exhibition+ExhibitionOneName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exhibition+ExhibitionTowName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exhibition+ExhibitionOneDesc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IconName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图片名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标服装</t>
+  </si>
+  <si>
+    <t>加成值</t>
+  </si>
+  <si>
+    <t>展会目标粉丝数</t>
   </si>
   <si>
     <t>CG_05.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TargetClothingID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标服装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AdditionValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加成值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName01</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc01</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName02</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc02</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName03</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc03</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName04</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc04</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName05</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc05</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName06</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc06</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName07</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc07</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName08</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc08</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionName09</t>
+  </si>
+  <si>
+    <t>Exhibition+ExhibitionDesc09</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -154,18 +180,348 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -173,30 +529,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -245,7 +887,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -280,7 +922,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -454,121 +1096,126 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="4" width="20.08203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="39.4140625" customWidth="1"/>
-    <col min="7" max="7" width="23.9140625" customWidth="1"/>
-    <col min="8" max="8" width="17.9140625" customWidth="1"/>
+    <col min="3" max="4" width="20.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="30.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="39.4166666666667" customWidth="1"/>
+    <col min="7" max="7" width="23.9166666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.9166666666667" customWidth="1"/>
+    <col min="9" max="9" width="18.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1">
         <v>10001</v>
@@ -576,47 +1223,227 @@
       <c r="H4" s="1">
         <v>1.2</v>
       </c>
+      <c r="I4">
+        <v>2000</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1">
+    <row r="5" ht="15" customHeight="1" spans="1:9">
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="H5" s="1">
         <v>1.2</v>
       </c>
+      <c r="I5">
+        <v>5000</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+    <row r="6" ht="13.5" customHeight="1" spans="1:9">
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10003</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I6">
+        <v>10000</v>
+      </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="B7" s="1"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+    <row r="7" spans="1:9">
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10004</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I7">
+        <v>30000</v>
+      </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+    <row r="8" spans="1:9">
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10005</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I8">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10006</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I9">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="1">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10007</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I10">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10008</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I11">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" s="1">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10009</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I12">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="1"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5762FB-7D02-45BB-B902-4152BEF9F308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FEDA40-0AC3-470D-BC9E-810C3D6AB74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="2100" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -153,6 +153,18 @@
   </si>
   <si>
     <t>Exhibition+ExhibitionDesc09</t>
+  </si>
+  <si>
+    <t>GameTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>展会游戏时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -201,13 +213,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -494,9 +509,10 @@
     <col min="6" max="6" width="23.9140625" customWidth="1"/>
     <col min="7" max="7" width="17.9140625" customWidth="1"/>
     <col min="8" max="8" width="18.58203125" customWidth="1"/>
+    <col min="9" max="9" width="14.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,8 +537,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -547,8 +566,11 @@
       <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -573,8 +595,11 @@
       <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -596,8 +621,11 @@
       <c r="H4" s="1">
         <v>2000</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1">
+      <c r="I4" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -619,8 +647,11 @@
       <c r="H5" s="1">
         <v>5000</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="13.5" customHeight="1">
+      <c r="I5" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="13.5" customHeight="1">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -642,8 +673,11 @@
       <c r="H6" s="1">
         <v>10000</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="B7" s="1">
         <v>4</v>
       </c>
@@ -665,8 +699,11 @@
       <c r="H7" s="1">
         <v>30000</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -688,8 +725,11 @@
       <c r="H8" s="1">
         <v>80000</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="B9" s="1">
         <v>6</v>
       </c>
@@ -711,8 +751,11 @@
       <c r="H9" s="1">
         <v>150000</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="B10" s="1">
         <v>7</v>
       </c>
@@ -734,8 +777,11 @@
       <c r="H10" s="1">
         <v>300000</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="B11" s="1">
         <v>8</v>
       </c>
@@ -757,8 +803,11 @@
       <c r="H11" s="1">
         <v>700000</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="B12" s="1">
         <v>9</v>
       </c>
@@ -780,8 +829,11 @@
       <c r="H12" s="1">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FEDA40-0AC3-470D-BC9E-810C3D6AB74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAC9842-C2EC-48ED-A9A9-E676336F8525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -164,6 +164,29 @@
   </si>
   <si>
     <t>展会游戏时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpdateInterval</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷新间隔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vector2</t>
+  </si>
+  <si>
+    <t>DwellTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>顾客停顿时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -171,7 +194,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +210,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -221,7 +252,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -499,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -510,9 +541,11 @@
     <col min="7" max="7" width="17.9140625" customWidth="1"/>
     <col min="8" max="8" width="18.58203125" customWidth="1"/>
     <col min="9" max="9" width="14.9140625" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,11 +570,17 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -566,11 +605,17 @@
       <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -595,11 +640,17 @@
       <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -624,8 +675,14 @@
       <c r="I4" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" customHeight="1">
+      <c r="J4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -650,8 +707,14 @@
       <c r="I5" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="13.5" customHeight="1">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -676,8 +739,14 @@
       <c r="I6" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="B7" s="1">
         <v>4</v>
       </c>
@@ -702,8 +771,14 @@
       <c r="I7" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -728,8 +803,14 @@
       <c r="I8" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="B9" s="1">
         <v>6</v>
       </c>
@@ -754,8 +835,14 @@
       <c r="I9" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="B10" s="1">
         <v>7</v>
       </c>
@@ -780,8 +867,14 @@
       <c r="I10" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="B11" s="1">
         <v>8</v>
       </c>
@@ -806,8 +899,14 @@
       <c r="I11" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="B12" s="1">
         <v>9</v>
       </c>
@@ -832,8 +931,14 @@
       <c r="I12" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAC9842-C2EC-48ED-A9A9-E676336F8525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBDE318-F901-4426-A223-F2D7AFE49616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5470" yWindow="480" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2300" yWindow="1100" windowWidth="35310" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -187,6 +187,18 @@
   </si>
   <si>
     <t>顾客停顿时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级时间所需接待数量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -244,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -253,6 +265,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -530,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -543,9 +558,10 @@
     <col min="9" max="9" width="14.9140625" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.58203125" customWidth="1"/>
+    <col min="12" max="12" width="25.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -579,8 +595,11 @@
       <c r="K1" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -614,8 +633,11 @@
       <c r="K2" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -649,8 +671,11 @@
       <c r="K3" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -681,8 +706,11 @@
       <c r="K4" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1">
+      <c r="L4" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -713,8 +741,11 @@
       <c r="K5" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="13.5" customHeight="1">
+      <c r="L5" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -745,8 +776,11 @@
       <c r="K6" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="B7" s="1">
         <v>4</v>
       </c>
@@ -777,8 +811,11 @@
       <c r="K7" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -809,8 +846,11 @@
       <c r="K8" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="B9" s="1">
         <v>6</v>
       </c>
@@ -841,8 +881,11 @@
       <c r="K9" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="B10" s="1">
         <v>7</v>
       </c>
@@ -873,8 +916,11 @@
       <c r="K10" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="B11" s="1">
         <v>8</v>
       </c>
@@ -905,8 +951,11 @@
       <c r="K11" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="B12" s="1">
         <v>9</v>
       </c>
@@ -937,8 +986,11 @@
       <c r="K12" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBDE318-F901-4426-A223-F2D7AFE49616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC7385B-49FA-4D78-8997-0ACA9F3EF0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2300" yWindow="1100" windowWidth="35310" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1100" windowWidth="35310" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -199,6 +199,14 @@
   </si>
   <si>
     <t>超级时间所需接待数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperTimer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超级时间持续时间</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -545,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -559,9 +567,10 @@
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.58203125" customWidth="1"/>
     <col min="12" max="12" width="25.9140625" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -598,8 +607,11 @@
       <c r="L1" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -633,11 +645,14 @@
       <c r="K2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -671,11 +686,14 @@
       <c r="K3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -709,8 +727,11 @@
       <c r="L4" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1">
+      <c r="M4" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -744,8 +765,11 @@
       <c r="L5" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="M5" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="13.5" customHeight="1">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -779,8 +803,11 @@
       <c r="L6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7" s="1">
         <v>4</v>
       </c>
@@ -814,8 +841,11 @@
       <c r="L7" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -849,8 +879,11 @@
       <c r="L8" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="B9" s="1">
         <v>6</v>
       </c>
@@ -884,8 +917,11 @@
       <c r="L9" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="B10" s="1">
         <v>7</v>
       </c>
@@ -919,8 +955,11 @@
       <c r="L10" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="B11" s="1">
         <v>8</v>
       </c>
@@ -954,8 +993,11 @@
       <c r="L11" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="B12" s="1">
         <v>9</v>
       </c>
@@ -989,8 +1031,11 @@
       <c r="L12" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="M12" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC7385B-49FA-4D78-8997-0ACA9F3EF0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677F44CF-4E70-4DB7-9EF7-545648934DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1100" windowWidth="35310" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -264,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -273,9 +273,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -648,7 +645,7 @@
       <c r="L2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -689,7 +686,7 @@
       <c r="L3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -728,7 +725,7 @@
         <v>5</v>
       </c>
       <c r="M4" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
@@ -766,7 +763,7 @@
         <v>5</v>
       </c>
       <c r="M5" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="13.5" customHeight="1">
@@ -804,7 +801,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -842,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="M7" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -880,7 +877,7 @@
         <v>5</v>
       </c>
       <c r="M8" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -918,7 +915,7 @@
         <v>5</v>
       </c>
       <c r="M9" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -956,7 +953,7 @@
         <v>5</v>
       </c>
       <c r="M10" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -994,7 +991,7 @@
         <v>5</v>
       </c>
       <c r="M11" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1032,7 +1029,7 @@
         <v>5</v>
       </c>
       <c r="M12" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:13">

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677F44CF-4E70-4DB7-9EF7-545648934DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE01B225-C706-426C-A641-BA0FBF67D93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1100" windowWidth="35310" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -207,6 +207,14 @@
   </si>
   <si>
     <t>超级时间持续时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoodwillValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感度增加</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -264,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -273,6 +281,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -550,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -567,7 +578,7 @@
     <col min="13" max="13" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,8 +618,11 @@
       <c r="M1" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -648,8 +662,11 @@
       <c r="M2" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -689,8 +706,11 @@
       <c r="M3" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -727,8 +747,11 @@
       <c r="M4" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1">
+      <c r="N4" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -765,8 +788,11 @@
       <c r="M5" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="13.5" customHeight="1">
+      <c r="N5" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="13.5" customHeight="1">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -803,8 +829,11 @@
       <c r="M6" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="B7" s="1">
         <v>4</v>
       </c>
@@ -841,8 +870,11 @@
       <c r="M7" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -879,8 +911,11 @@
       <c r="M8" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="B9" s="1">
         <v>6</v>
       </c>
@@ -917,8 +952,11 @@
       <c r="M9" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="B10" s="1">
         <v>7</v>
       </c>
@@ -955,8 +993,11 @@
       <c r="M10" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="B11" s="1">
         <v>8</v>
       </c>
@@ -993,8 +1034,11 @@
       <c r="M11" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12" s="1">
         <v>9</v>
       </c>
@@ -1031,8 +1075,11 @@
       <c r="M12" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ExhibitionInfoData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE01B225-C706-426C-A641-BA0FBF67D93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -59,6 +53,24 @@
     <t>ExhibitionTargetFans</t>
   </si>
   <si>
+    <t>GameTime</t>
+  </si>
+  <si>
+    <t>UpdateInterval</t>
+  </si>
+  <si>
+    <t>DwellTime</t>
+  </si>
+  <si>
+    <t>SuperCount</t>
+  </si>
+  <si>
+    <t>SuperTimer</t>
+  </si>
+  <si>
+    <t>GoodwillValue</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -74,6 +86,12 @@
     <t>float</t>
   </si>
   <si>
+    <t>vector2</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -98,6 +116,24 @@
     <t>展会目标粉丝数</t>
   </si>
   <si>
+    <t>展会游戏时间</t>
+  </si>
+  <si>
+    <t>刷新间隔</t>
+  </si>
+  <si>
+    <t>顾客停顿时间</t>
+  </si>
+  <si>
+    <t>超级时间所需接待数量</t>
+  </si>
+  <si>
+    <t>超级时间持续时间</t>
+  </si>
+  <si>
+    <t>好感度上限增加</t>
+  </si>
+  <si>
     <t>CG_05.png</t>
   </si>
   <si>
@@ -107,6 +143,9 @@
     <t>Exhibition+ExhibitionDesc01</t>
   </si>
   <si>
+    <t>3,5</t>
+  </si>
+  <si>
     <t>Exhibition+ExhibitionName02</t>
   </si>
   <si>
@@ -153,76 +192,26 @@
   </si>
   <si>
     <t>Exhibition+ExhibitionDesc09</t>
-  </si>
-  <si>
-    <t>GameTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>展会游戏时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpdateInterval</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>刷新间隔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>vector2</t>
-  </si>
-  <si>
-    <t>DwellTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>顾客停顿时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>超级时间所需接待数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperTimer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>超级时间持续时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GoodwillValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>好感度增加</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,33 +223,348 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -268,36 +572,322 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -555,27 +1145,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="20.08203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="39.4140625" customWidth="1"/>
-    <col min="6" max="6" width="23.9140625" customWidth="1"/>
-    <col min="7" max="7" width="17.9140625" customWidth="1"/>
-    <col min="8" max="8" width="18.58203125" customWidth="1"/>
-    <col min="9" max="9" width="14.9140625" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.58203125" customWidth="1"/>
-    <col min="12" max="12" width="25.9140625" customWidth="1"/>
+    <col min="3" max="3" width="20.0833333333333" customWidth="1"/>
+    <col min="4" max="4" width="30.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="39.4166666666667" customWidth="1"/>
+    <col min="6" max="6" width="23.9166666666667" customWidth="1"/>
+    <col min="7" max="7" width="17.9166666666667" customWidth="1"/>
+    <col min="8" max="8" width="18.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="14.9166666666667" customWidth="1"/>
+    <col min="10" max="10" width="18.8333333333333" customWidth="1"/>
+    <col min="11" max="11" width="15.5833333333333" customWidth="1"/>
+    <col min="12" max="12" width="25.9166666666667" customWidth="1"/>
     <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="14" max="14" width="14.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -604,124 +1195,124 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>54</v>
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>46</v>
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
+      <c r="C4" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F4" s="1">
         <v>10001</v>
@@ -733,36 +1324,36 @@
         <v>2000</v>
       </c>
       <c r="I4" s="1">
-        <v>300</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="3">
-        <v>30</v>
-      </c>
-      <c r="L4" s="3">
+        <v>120</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="2">
+        <v>30</v>
+      </c>
+      <c r="L4" s="2">
         <v>5</v>
       </c>
-      <c r="M4" s="3">
-        <v>30</v>
-      </c>
-      <c r="N4" s="3">
-        <v>10</v>
+      <c r="M4" s="2">
+        <v>30</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1">
+    <row r="5" ht="15" customHeight="1" spans="1:14">
       <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>21</v>
+      <c r="C5" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1">
         <v>10002</v>
@@ -774,36 +1365,36 @@
         <v>5000</v>
       </c>
       <c r="I5" s="1">
-        <v>300</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="3">
-        <v>30</v>
-      </c>
-      <c r="L5" s="3">
+        <v>120</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="2">
+        <v>30</v>
+      </c>
+      <c r="L5" s="2">
         <v>5</v>
       </c>
-      <c r="M5" s="3">
-        <v>30</v>
-      </c>
-      <c r="N5" s="3">
-        <v>10</v>
+      <c r="M5" s="2">
+        <v>30</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5" customHeight="1">
+    <row r="6" ht="13.5" customHeight="1" spans="1:14">
       <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
+      <c r="C6" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F6" s="1">
         <v>10003</v>
@@ -815,36 +1406,36 @@
         <v>10000</v>
       </c>
       <c r="I6" s="1">
-        <v>300</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="3">
-        <v>30</v>
-      </c>
-      <c r="L6" s="3">
+        <v>120</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="2">
+        <v>30</v>
+      </c>
+      <c r="L6" s="2">
         <v>5</v>
       </c>
-      <c r="M6" s="3">
-        <v>30</v>
-      </c>
-      <c r="N6" s="3">
-        <v>10</v>
+      <c r="M6" s="2">
+        <v>30</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="1">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
+      <c r="C7" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F7" s="1">
         <v>10004</v>
@@ -856,36 +1447,36 @@
         <v>30000</v>
       </c>
       <c r="I7" s="1">
-        <v>300</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="3">
-        <v>30</v>
-      </c>
-      <c r="L7" s="3">
+        <v>120</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="2">
+        <v>30</v>
+      </c>
+      <c r="L7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="3">
-        <v>30</v>
-      </c>
-      <c r="N7" s="3">
-        <v>10</v>
+      <c r="M7" s="2">
+        <v>30</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="B8" s="1">
         <v>5</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>21</v>
+      <c r="C8" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1">
         <v>10005</v>
@@ -897,36 +1488,36 @@
         <v>80000</v>
       </c>
       <c r="I8" s="1">
-        <v>300</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="3">
-        <v>30</v>
-      </c>
-      <c r="L8" s="3">
+        <v>120</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="2">
+        <v>30</v>
+      </c>
+      <c r="L8" s="2">
         <v>5</v>
       </c>
-      <c r="M8" s="3">
-        <v>30</v>
-      </c>
-      <c r="N8" s="3">
-        <v>10</v>
+      <c r="M8" s="2">
+        <v>30</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="B9" s="1">
         <v>6</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>21</v>
+      <c r="C9" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1">
         <v>10006</v>
@@ -938,36 +1529,36 @@
         <v>150000</v>
       </c>
       <c r="I9" s="1">
-        <v>300</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="3">
-        <v>30</v>
-      </c>
-      <c r="L9" s="3">
+        <v>120</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="2">
+        <v>30</v>
+      </c>
+      <c r="L9" s="2">
         <v>5</v>
       </c>
-      <c r="M9" s="3">
-        <v>30</v>
-      </c>
-      <c r="N9" s="3">
-        <v>10</v>
+      <c r="M9" s="2">
+        <v>30</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="B10" s="1">
         <v>7</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>21</v>
+      <c r="C10" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F10" s="1">
         <v>10007</v>
@@ -979,36 +1570,36 @@
         <v>300000</v>
       </c>
       <c r="I10" s="1">
-        <v>300</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="3">
-        <v>30</v>
-      </c>
-      <c r="L10" s="3">
+        <v>120</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="2">
+        <v>30</v>
+      </c>
+      <c r="L10" s="2">
         <v>5</v>
       </c>
-      <c r="M10" s="3">
-        <v>30</v>
-      </c>
-      <c r="N10" s="3">
-        <v>10</v>
+      <c r="M10" s="2">
+        <v>30</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="B11" s="1">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F11" s="1">
         <v>10008</v>
@@ -1020,36 +1611,36 @@
         <v>700000</v>
       </c>
       <c r="I11" s="1">
-        <v>300</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" s="3">
-        <v>30</v>
-      </c>
-      <c r="L11" s="3">
+        <v>120</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="2">
+        <v>30</v>
+      </c>
+      <c r="L11" s="2">
         <v>5</v>
       </c>
-      <c r="M11" s="3">
-        <v>30</v>
-      </c>
-      <c r="N11" s="3">
-        <v>10</v>
+      <c r="M11" s="2">
+        <v>30</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="B12" s="1">
         <v>9</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
+      <c r="C12" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F12" s="1">
         <v>10009</v>
@@ -1061,33 +1652,33 @@
         <v>10000000</v>
       </c>
       <c r="I12" s="1">
-        <v>300</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="3">
-        <v>30</v>
-      </c>
-      <c r="L12" s="3">
+        <v>120</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" s="2">
+        <v>30</v>
+      </c>
+      <c r="L12" s="2">
         <v>5</v>
       </c>
-      <c r="M12" s="3">
-        <v>30</v>
-      </c>
-      <c r="N12" s="3">
-        <v>10</v>
+      <c r="M12" s="2">
+        <v>30</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="1"/>
-      <c r="C13" s="2"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>